--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2019_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2019_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:36</t>
+    <t xml:space="preserve">2026-09-09 22:21</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2019_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2019_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:21</t>
+    <t xml:space="preserve">2026-09-12 19:38</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2019_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2019_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:38</t>
+    <t xml:space="preserve">2026-09-24 00:15</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2019_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2019_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:15</t>
+    <t xml:space="preserve">2026-09-27 22:05</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2019_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2019_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 22:05</t>
+    <t xml:space="preserve">2026-09-29 10:59</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -544,7 +544,7 @@
         <v>2019</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>33.68</v>
+        <v>336.81</v>
       </c>
     </row>
     <row r="3">
@@ -561,7 +561,7 @@
         <v>2019</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>28.42</v>
+        <v>284.24</v>
       </c>
     </row>
     <row r="4">
@@ -578,7 +578,7 @@
         <v>2019</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>27.79</v>
+        <v>277.85</v>
       </c>
     </row>
     <row r="5">
@@ -595,7 +595,7 @@
         <v>2019</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>27.24</v>
+        <v>272.44</v>
       </c>
     </row>
     <row r="6">
@@ -612,7 +612,7 @@
         <v>2019</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>23.43</v>
+        <v>234.25</v>
       </c>
     </row>
     <row r="7">
@@ -629,7 +629,7 @@
         <v>2019</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>23.32</v>
+        <v>233.22</v>
       </c>
     </row>
     <row r="8">
@@ -646,7 +646,7 @@
         <v>2019</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>21.71</v>
+        <v>217.07</v>
       </c>
     </row>
     <row r="9">
@@ -663,7 +663,7 @@
         <v>2019</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>19.93</v>
+        <v>199.27</v>
       </c>
     </row>
     <row r="10">
@@ -680,7 +680,7 @@
         <v>2019</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>19.69</v>
+        <v>196.87</v>
       </c>
     </row>
     <row r="11">
@@ -697,7 +697,7 @@
         <v>2019</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>18.39</v>
+        <v>183.85</v>
       </c>
     </row>
     <row r="12">
@@ -714,7 +714,7 @@
         <v>2019</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>17.64</v>
+        <v>176.4</v>
       </c>
     </row>
     <row r="13">
@@ -731,7 +731,7 @@
         <v>2019</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>17.63</v>
+        <v>176.35</v>
       </c>
     </row>
     <row r="14">
@@ -748,7 +748,7 @@
         <v>2019</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>17.57</v>
+        <v>175.67</v>
       </c>
     </row>
     <row r="15">
@@ -765,7 +765,7 @@
         <v>2019</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>16.95</v>
+        <v>169.51</v>
       </c>
     </row>
     <row r="16">
@@ -782,7 +782,7 @@
         <v>2019</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>16.91</v>
+        <v>169.15</v>
       </c>
     </row>
     <row r="17">
@@ -799,7 +799,7 @@
         <v>2019</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>16.68</v>
+        <v>166.8</v>
       </c>
     </row>
     <row r="18">
@@ -816,7 +816,7 @@
         <v>2019</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>16.23</v>
+        <v>162.27</v>
       </c>
     </row>
     <row r="19">
@@ -833,7 +833,7 @@
         <v>2019</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>15.74</v>
+        <v>157.41</v>
       </c>
     </row>
     <row r="20">
@@ -850,7 +850,7 @@
         <v>2019</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>15.46</v>
+        <v>154.58</v>
       </c>
     </row>
     <row r="21">
@@ -867,7 +867,7 @@
         <v>2019</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>14.86</v>
+        <v>148.61</v>
       </c>
     </row>
     <row r="22">
@@ -884,7 +884,7 @@
         <v>2019</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>14.82</v>
+        <v>148.2</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2019_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2019_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 10:59</t>
+    <t xml:space="preserve">2026-10-01 19:24</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -126,7 +126,7 @@
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Unidad territorial</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2019_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2019_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 19:24</t>
+    <t xml:space="preserve">2026-10-02 13:15</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2019_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2019_nuble.xlsx
@@ -48,7 +48,7 @@
     <t xml:space="preserve">San Fabián</t>
   </si>
   <si>
-    <t xml:space="preserve">Ranquil</t>
+    <t xml:space="preserve">Ránquil</t>
   </si>
   <si>
     <t xml:space="preserve">Treguaco</t>
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:15</t>
+    <t xml:space="preserve">2026-10-04 07:54</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2019_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2019_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 07:54</t>
+    <t xml:space="preserve">2026-10-05 07:18</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
